--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/aysen.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/aysen.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>71677.44</v>
+        <v>71285.66</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>37429.46</v>
+        <v>37224.48</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>57395.09</v>
+        <v>57808.88</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>21497.76</v>
+        <v>21467.6</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>55324.7</v>
+        <v>54910.65</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>45103.17</v>
+        <v>44983.88</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>78885.42999999999</v>
+        <v>77264.2</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>73244.25</v>
+        <v>72820.3</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>712.6799999999999</v>
+        <v>708.55</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/aysen.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/aysen.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4609-526-CM25</t>
+          <t>2494-83-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>DERCOMAQ SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.545.450-0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>71285.66</v>
+        <v>29352.76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4144-152-CM25</t>
+          <t>657-47-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.253.000-4</t>
+          <t>61.823.000-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION XI REGION</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>37224.48</v>
+        <v>25214.77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4144-160-CM25</t>
+          <t>1428275-39-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.253.000-4</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>57808.88</v>
+        <v>24334.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1233615-12078-CM25</t>
+          <t>657-183-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.823.000-7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION XI REGION</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>21467.6</v>
+        <v>26032.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>697209-4-CM26</t>
+          <t>4609-526-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,43 +813,43 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>54910.65</v>
+        <v>71285.66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2713-684-CM26</t>
+          <t>4144-152-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.253.000-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>44983.88</v>
+        <v>37224.48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1286987-18-CM26</t>
+          <t>4144-160-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.797.310-6</t>
+          <t>69.253.000-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Deportes y Recreación Coy</t>
+          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,43 +935,43 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>77264.2</v>
+        <v>57808.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1195-408-CM26</t>
+          <t>1233615-12078-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,43 +996,43 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>72820.3</v>
+        <v>21467.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1195-409-CM26</t>
+          <t>697209-4-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,6 +1057,250 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
+        <v>54910.65</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2713-684-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>44983.88</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1286987-18-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>65.797.310-6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Corporación Municipal de Deportes y Recreación Coy</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>77264.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1195-408-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>72820.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1195-409-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
         <v>708.55</v>
       </c>
     </row>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/aysen.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Deportes y Recreación Coy</t>
+          <t>Corporación Municipal de Deportes y Recreación Coyhaique</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1302,6 +1302,67 @@
       </c>
       <c r="M14" s="2" t="n">
         <v>708.55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>657-128-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.823.000-7</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION XI REGION</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>28005.52</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/aysen.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/aysen.xlsx
@@ -562,7 +562,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/aysen.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1403,6 +1403,67 @@
       </c>
       <c r="M15" s="2" t="n">
         <v>28005.52</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1344158-26-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>60.511.110-6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>FINNING CHILE S A</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>91.489.000-4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>101829.9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/aysen.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/aysen.xlsx
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
